--- a/scenes/metadata_audit.xlsx
+++ b/scenes/metadata_audit.xlsx
@@ -624,7 +624,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -634,6 +634,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -956,7 +962,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -980,16 +986,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -998,93 +1004,96 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4181,29 +4190,29 @@
         <v>26</v>
       </c>
     </row>
-    <row r="99" spans="1:8">
-      <c r="A99" t="s">
+    <row r="99" s="2" customFormat="1" spans="1:8">
+      <c r="A99" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B99" t="b">
-        <v>0</v>
-      </c>
-      <c r="C99" t="b">
-        <v>0</v>
-      </c>
-      <c r="D99" t="b">
-        <v>0</v>
-      </c>
-      <c r="E99" t="s">
-        <v>17</v>
-      </c>
-      <c r="F99">
-        <v>0</v>
-      </c>
-      <c r="G99" t="s">
+      <c r="B99" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="C99" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D99" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F99" s="2">
+        <v>0</v>
+      </c>
+      <c r="G99" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H99" t="s">
+      <c r="H99" s="2" t="s">
         <v>18</v>
       </c>
     </row>
